--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.28448601285933</v>
+        <v>6.871228977089642</v>
       </c>
       <c r="D2" t="n">
-        <v>57.20140679152502</v>
+        <v>9.295228603622816</v>
       </c>
       <c r="E2" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F2" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.60544623330215</v>
+        <v>2.048385012911599</v>
       </c>
       <c r="D3" t="n">
-        <v>14.6924532593544</v>
+        <v>2.38752365464509</v>
       </c>
       <c r="E3" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F3" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1.600488241601019</v>
+        <v>0.2600793392601656</v>
       </c>
       <c r="D4" t="n">
-        <v>3.467444136023464</v>
+        <v>0.5634596721038129</v>
       </c>
       <c r="E4" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F4" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.33395361505196</v>
+        <v>2.004267462445943</v>
       </c>
       <c r="D5" t="n">
-        <v>10.61776449481343</v>
+        <v>1.725386730407183</v>
       </c>
       <c r="E5" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F5" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.86945066911094</v>
+        <v>5.016285733730528</v>
       </c>
       <c r="D6" t="n">
-        <v>28.9414732320106</v>
+        <v>4.702989400201723</v>
       </c>
       <c r="E6" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F6" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.7525457559854</v>
+        <v>9.222288685347628</v>
       </c>
       <c r="D7" t="n">
-        <v>54.77596699922748</v>
+        <v>8.901094637374465</v>
       </c>
       <c r="E7" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F7" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.39402227199577</v>
+        <v>5.589028619199313</v>
       </c>
       <c r="D8" t="n">
-        <v>32.36958954224665</v>
+        <v>5.260058300615081</v>
       </c>
       <c r="E8" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F8" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.76808504077429</v>
+        <v>7.112313819125822</v>
       </c>
       <c r="D9" t="n">
-        <v>41.75775825154835</v>
+        <v>6.785635715876606</v>
       </c>
       <c r="E9" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F9" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.58372733568397</v>
+        <v>5.619855692048646</v>
       </c>
       <c r="D10" t="n">
-        <v>41.64134152314191</v>
+        <v>6.766717997510561</v>
       </c>
       <c r="E10" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F10" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>57.97648795364955</v>
+        <v>9.421179292468052</v>
       </c>
       <c r="D11" t="n">
-        <v>55.98734760166171</v>
+        <v>9.097943985270028</v>
       </c>
       <c r="E11" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F11" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>52.57255239157707</v>
+        <v>8.543039763631274</v>
       </c>
       <c r="D12" t="n">
-        <v>50.73712030157666</v>
+        <v>8.244782049006208</v>
       </c>
       <c r="E12" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F12" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>45.6370782246941</v>
+        <v>7.416025211512792</v>
       </c>
       <c r="D13" t="n">
-        <v>51.9854527125645</v>
+        <v>8.447636065791732</v>
       </c>
       <c r="E13" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F13" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>79.5838525015607</v>
+        <v>12.93237603150361</v>
       </c>
       <c r="D14" t="n">
-        <v>77.54502633574114</v>
+        <v>12.60106677955794</v>
       </c>
       <c r="E14" t="n">
-        <v>20.56336434989986</v>
+        <v>3.341546706858726</v>
       </c>
       <c r="F14" t="n">
-        <v>20.49927638698317</v>
+        <v>3.331132412884765</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
